--- a/R_Codes/DataSummary/Archaea/Sample_name/Archaea_Summary_Class_by_Sample_name.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_name/Archaea_Summary_Class_by_Sample_name.xlsx
@@ -463,10 +463,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>37.5918082071325</v>
+        <v>37.6083286086558</v>
       </c>
       <c r="D2" t="n">
-        <v>5.59724283853563</v>
+        <v>5.60163716781323</v>
       </c>
     </row>
     <row r="3">
@@ -477,10 +477,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>19.2288487135942</v>
+        <v>19.218471533848</v>
       </c>
       <c r="D3" t="n">
-        <v>2.24433712249579</v>
+        <v>2.2429594916445</v>
       </c>
     </row>
     <row r="4">
@@ -491,10 +491,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>11.8220727936251</v>
+        <v>11.8162315611905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.242385998194631</v>
+        <v>0.242172248980803</v>
       </c>
     </row>
     <row r="5">
@@ -505,10 +505,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>8.87422557441279</v>
+        <v>8.87367336866335</v>
       </c>
       <c r="D5" t="n">
-        <v>1.07596066206467</v>
+        <v>1.07583848042334</v>
       </c>
     </row>
     <row r="6">
@@ -519,10 +519,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>8.09463516172468</v>
+        <v>8.09618084032267</v>
       </c>
       <c r="D6" t="n">
-        <v>1.77500895016411</v>
+        <v>1.77463760386218</v>
       </c>
     </row>
     <row r="7">
@@ -533,10 +533,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>4.26967222633716</v>
+        <v>4.26749999551657</v>
       </c>
       <c r="D7" t="n">
-        <v>0.136065425139798</v>
+        <v>0.136006692264525</v>
       </c>
     </row>
     <row r="8">
@@ -547,10 +547,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>3.85724314325943</v>
+        <v>3.85659997602783</v>
       </c>
       <c r="D8" t="n">
-        <v>0.258814485668615</v>
+        <v>0.258727160048228</v>
       </c>
     </row>
     <row r="9">
@@ -561,10 +561,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1.614157665827</v>
+        <v>1.61344272707602</v>
       </c>
       <c r="D9" t="n">
-        <v>0.789400869514276</v>
+        <v>0.789053066778589</v>
       </c>
     </row>
     <row r="10">
@@ -575,10 +575,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>1.60491681905068</v>
+        <v>1.60475341957924</v>
       </c>
       <c r="D10" t="n">
-        <v>0.203347398935847</v>
+        <v>0.203320697582051</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>1.37355874984232</v>
+        <v>1.37632070583837</v>
       </c>
       <c r="D11" t="n">
-        <v>0.608027825036764</v>
+        <v>0.609441380320974</v>
       </c>
     </row>
     <row r="12">
@@ -603,10 +603,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>0.488304591428244</v>
+        <v>0.487974196393938</v>
       </c>
       <c r="D12" t="n">
-        <v>0.328954556158683</v>
+        <v>0.328723155057284</v>
       </c>
     </row>
     <row r="13">
@@ -617,10 +617,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.477247905242917</v>
+        <v>0.477051715520837</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0450023147999319</v>
+        <v>0.0449831141801297</v>
       </c>
     </row>
     <row r="14">
@@ -631,10 +631,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.270575615186224</v>
+        <v>0.270468621631591</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0205268698885638</v>
+        <v>0.0205094904998427</v>
       </c>
     </row>
     <row r="15">
@@ -645,7 +645,7 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>0.115689526293467</v>
+        <v>0.115783032995387</v>
       </c>
       <c r="D15"/>
     </row>
@@ -657,10 +657,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.10336839725838</v>
+        <v>0.10349339817975</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0254780013641728</v>
+        <v>0.0254968433941032</v>
       </c>
     </row>
     <row r="17">
@@ -671,10 +671,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0991157658669333</v>
+        <v>0.0991442804136611</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0174851506219885</v>
+        <v>0.0174930856340913</v>
       </c>
     </row>
     <row r="18">
@@ -685,10 +685,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0836277009911762</v>
+        <v>0.0836599616266827</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0227641652334727</v>
+        <v>0.0227635062895201</v>
       </c>
     </row>
     <row r="19">
@@ -699,7 +699,7 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0130089175550854</v>
+        <v>0.0129953377876777</v>
       </c>
       <c r="D19"/>
     </row>
@@ -711,7 +711,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00982099833583932</v>
+        <v>0.00983170785250912</v>
       </c>
       <c r="D20"/>
     </row>
@@ -723,7 +723,7 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00632532289747537</v>
+        <v>0.00631872001038943</v>
       </c>
       <c r="D21"/>
     </row>
@@ -735,7 +735,7 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00177620413836834</v>
+        <v>0.00177629086912041</v>
       </c>
       <c r="D22"/>
     </row>
@@ -772,10 +772,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>59.7972040101877</v>
+        <v>60.0117510250063</v>
       </c>
       <c r="D2" t="n">
-        <v>18.976589310687</v>
+        <v>19.0438950283452</v>
       </c>
     </row>
     <row r="3">
@@ -786,10 +786,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>32.1764152523528</v>
+        <v>32.072524514091</v>
       </c>
       <c r="D3" t="n">
-        <v>0.326105319199372</v>
+        <v>0.324979573100751</v>
       </c>
     </row>
     <row r="4">
@@ -800,10 +800,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>1.93891184712223</v>
+        <v>1.93261553258066</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0663761273090235</v>
+        <v>0.0661212506766528</v>
       </c>
     </row>
     <row r="5">
@@ -814,10 +814,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>1.73075091445215</v>
+        <v>1.72381281041984</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0592720139891462</v>
+        <v>0.0588899026502082</v>
       </c>
     </row>
     <row r="6">
@@ -828,10 +828,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>1.32331005636933</v>
+        <v>1.26449200613915</v>
       </c>
       <c r="D6" t="n">
-        <v>0.310923335917212</v>
+        <v>0.293011298259827</v>
       </c>
     </row>
     <row r="7">
@@ -842,10 +842,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0.954502856650244</v>
+        <v>0.951599115313579</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0704228505917791</v>
+        <v>0.0702002637596548</v>
       </c>
     </row>
     <row r="8">
@@ -856,10 +856,10 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>0.918635764339107</v>
+        <v>0.888043173298091</v>
       </c>
       <c r="D8" t="n">
-        <v>0.160565559093251</v>
+        <v>0.15131718509958</v>
       </c>
     </row>
     <row r="9">
@@ -870,10 +870,10 @@
         <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>0.471306513325133</v>
+        <v>0.470088527818709</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0164315430986118</v>
+        <v>0.0163901011625428</v>
       </c>
     </row>
     <row r="10">
@@ -884,10 +884,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.402296245812782</v>
+        <v>0.401484811843114</v>
       </c>
       <c r="D10" t="n">
-        <v>0.274871069987508</v>
+        <v>0.274321679413749</v>
       </c>
     </row>
     <row r="11">
@@ -898,10 +898,10 @@
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>0.132284452778502</v>
+        <v>0.13250593027904</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0278585800252594</v>
+        <v>0.0279680233633284</v>
       </c>
     </row>
     <row r="12">
@@ -912,10 +912,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>0.108520301484974</v>
+        <v>0.105343591806292</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0146072490474575</v>
+        <v>0.0136460636697803</v>
       </c>
     </row>
     <row r="13">
@@ -926,10 +926,10 @@
         <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0151854301157901</v>
+        <v>0.015146783271896</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00296997966832071</v>
+        <v>0.00296250525510009</v>
       </c>
     </row>
     <row r="14">
@@ -940,7 +940,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00743107690211342</v>
+        <v>0.00741230379725906</v>
       </c>
       <c r="D14"/>
     </row>
@@ -952,10 +952,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>0.00676741122361874</v>
+        <v>0.0067439889623678</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00285785858713188</v>
+        <v>0.00284210346859634</v>
       </c>
     </row>
     <row r="16">
@@ -966,7 +966,7 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00613877383033067</v>
+        <v>0.00612320169641204</v>
       </c>
       <c r="D16"/>
     </row>
@@ -978,7 +978,7 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00452332814272972</v>
+        <v>0.00451179078774197</v>
       </c>
       <c r="D17"/>
     </row>
@@ -990,7 +990,7 @@
         <v>29</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00452332814272972</v>
+        <v>0.00451179078774197</v>
       </c>
       <c r="D18"/>
     </row>
@@ -1002,7 +1002,7 @@
         <v>30</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0012924367675278</v>
+        <v>0.00128910210084702</v>
       </c>
       <c r="D19"/>
     </row>
@@ -1039,10 +1039,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>18.5202533685736</v>
+        <v>18.5201013097571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.505976770488784</v>
+        <v>0.505976909932865</v>
       </c>
     </row>
     <row r="3">
@@ -1053,10 +1053,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>16.7496098664917</v>
+        <v>16.7453301923525</v>
       </c>
       <c r="D3" t="n">
-        <v>2.96408088351006</v>
+        <v>2.9630776468081</v>
       </c>
     </row>
     <row r="4">
@@ -1067,10 +1067,10 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>12.6800338133721</v>
+        <v>12.6804160381113</v>
       </c>
       <c r="D4" t="n">
-        <v>0.423578860668056</v>
+        <v>0.423591198619781</v>
       </c>
     </row>
     <row r="5">
@@ -1081,10 +1081,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>12.3021921641972</v>
+        <v>12.3026594588541</v>
       </c>
       <c r="D5" t="n">
-        <v>0.680026350575475</v>
+        <v>0.680014840542453</v>
       </c>
     </row>
     <row r="6">
@@ -1095,10 +1095,10 @@
         <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>11.7452341318612</v>
+        <v>11.7458348323098</v>
       </c>
       <c r="D6" t="n">
-        <v>1.37682566368649</v>
+        <v>1.37689345146925</v>
       </c>
     </row>
     <row r="7">
@@ -1109,10 +1109,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>6.95538214449839</v>
+        <v>6.95653878385309</v>
       </c>
       <c r="D7" t="n">
-        <v>0.051641360466749</v>
+        <v>0.0516579124591188</v>
       </c>
     </row>
     <row r="8">
@@ -1123,10 +1123,10 @@
         <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>6.25422579699541</v>
+        <v>6.25509725438493</v>
       </c>
       <c r="D8" t="n">
-        <v>3.99436845805551</v>
+        <v>3.99503421260845</v>
       </c>
     </row>
     <row r="9">
@@ -1137,10 +1137,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>6.11588517287203</v>
+        <v>6.1164324484389</v>
       </c>
       <c r="D9" t="n">
-        <v>0.616074763446808</v>
+        <v>0.616147299562352</v>
       </c>
     </row>
     <row r="10">
@@ -1151,10 +1151,10 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>2.19994636630155</v>
+        <v>2.1998961256231</v>
       </c>
       <c r="D10" t="n">
-        <v>0.107160564694792</v>
+        <v>0.107160590329108</v>
       </c>
     </row>
     <row r="11">
@@ -1165,10 +1165,10 @@
         <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>1.46754394593324</v>
+        <v>1.46756821441988</v>
       </c>
       <c r="D11" t="n">
-        <v>0.221908676469357</v>
+        <v>0.221914596352504</v>
       </c>
     </row>
     <row r="12">
@@ -1179,10 +1179,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>1.46564892526542</v>
+        <v>1.46612663342029</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0466877372539877</v>
+        <v>0.0467043258433747</v>
       </c>
     </row>
     <row r="13">
@@ -1193,10 +1193,10 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>0.939262261327925</v>
+        <v>0.939235706664847</v>
       </c>
       <c r="D13" t="n">
-        <v>0.076588972054449</v>
+        <v>0.0765853287362225</v>
       </c>
     </row>
     <row r="14">
@@ -1207,10 +1207,10 @@
         <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>0.922485621046044</v>
+        <v>0.922428448465171</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0956601710709274</v>
+        <v>0.0956434026846114</v>
       </c>
     </row>
     <row r="15">
@@ -1221,10 +1221,10 @@
         <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>0.702726037156627</v>
+        <v>0.702697770525482</v>
       </c>
       <c r="D15" t="n">
-        <v>0.187953862659956</v>
+        <v>0.187943863450388</v>
       </c>
     </row>
     <row r="16">
@@ -1235,10 +1235,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>0.373053088548069</v>
+        <v>0.373104243580127</v>
       </c>
       <c r="D16" t="n">
-        <v>0.115024472265287</v>
+        <v>0.115042827780335</v>
       </c>
     </row>
     <row r="17">
@@ -1249,10 +1249,10 @@
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>0.140690285136584</v>
+        <v>0.140685141227975</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0128404769835274</v>
+        <v>0.0128378141578971</v>
       </c>
     </row>
     <row r="18">
@@ -1263,10 +1263,10 @@
         <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>0.139326797297523</v>
+        <v>0.139357882061933</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00657364646947169</v>
+        <v>0.00657574523047377</v>
       </c>
     </row>
     <row r="19">
@@ -1277,10 +1277,10 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>0.114960544008385</v>
+        <v>0.114961862604409</v>
       </c>
       <c r="D19" t="n">
-        <v>0.032622598907635</v>
+        <v>0.0326241618178361</v>
       </c>
     </row>
     <row r="20">
@@ -1291,10 +1291,10 @@
         <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0803675904299304</v>
+        <v>0.08037041417289</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0353534956882546</v>
+        <v>0.0353555078309078</v>
       </c>
     </row>
     <row r="21">
@@ -1305,10 +1305,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0757661709457359</v>
+        <v>0.0757499067335201</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0524181217803904</v>
+        <v>0.0524055170092779</v>
       </c>
     </row>
     <row r="22">
@@ -1319,7 +1319,7 @@
         <v>29</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0301708776892948</v>
+        <v>0.0301647251607637</v>
       </c>
       <c r="D22"/>
     </row>
@@ -1331,7 +1331,7 @@
         <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0230510669255519</v>
+        <v>0.0230564187299055</v>
       </c>
       <c r="D23"/>
     </row>
@@ -1343,7 +1343,7 @@
         <v>32</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00218396312648901</v>
+        <v>0.00218618854804676</v>
       </c>
       <c r="D24"/>
     </row>
